--- a/ML25051A096.xlsx
+++ b/ML25051A096.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Under Construction" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operating Reactors'!$A$1:$T$95</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Under Construction'!$A$1:$P$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Operating Reactors'!$A$1:$V$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Under Construction'!$A$1:$R$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T95"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -478,17 +478,19 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="46" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -539,55 +541,65 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>FIPS Code</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Architect Engineer</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Constructor</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>License Number</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Docket Number</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CP Issued</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>OL Issued</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Comm. Op</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>LR Issued</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SR Issued</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Exp. Date</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NRC Web Page</t>
         </is>
@@ -641,55 +653,65 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>Pope County</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>05115</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>DPR-51</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>05000313</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>12/06/1968</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>05/21/1974</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>12/19/1974</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>06/20/2001</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>05/20/2034</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/ano1.html</t>
         </is>
@@ -743,55 +765,65 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
+          <t>Pope County</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>05115</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>NPF-6</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>05000368</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>12/06/1972</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>09/01/1978</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>03/26/1980</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>06/30/2005</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>07/17/2038</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/ano2.html</t>
         </is>
@@ -845,55 +877,65 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>Beaver County</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>42007</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>DPR-66</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>05000334</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>06/26/1970</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>07/02/1976</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>10/01/1976</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>11/05/2009</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>01/29/2036</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/bv1.html</t>
         </is>
@@ -947,55 +989,65 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
+          <t>Beaver County</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>42007</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>NPF-73</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>05000412</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>05/03/1974</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>08/14/1987</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>11/17/1987</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>11/05/2009</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>05/27/2047</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/bv2.html</t>
         </is>
@@ -1049,55 +1101,65 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>Will County</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>17197</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>CWE</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>NPF-72</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>05000456</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>12/31/1975</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>07/02/1987</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>07/29/1988</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>01/27/2016</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>10/17/2046</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/brai1.html</t>
         </is>
@@ -1151,55 +1213,65 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
+          <t>Will County</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>17197</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>CWE</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>NPF-77</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>05000457</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>12/31/1975</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>05/20/1988</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>10/17/1988</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>01/27/2016</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>12/18/2047</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/brai2.html</t>
         </is>
@@ -1253,55 +1325,65 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>Limestone County</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>01083</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>DPR-33</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>05000259</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>05/10/1967</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>12/20/1973</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>08/01/1974</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>05/04/2006</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>12/20/2033</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/bf1.html</t>
         </is>
@@ -1355,55 +1437,65 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
+          <t>Limestone County</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>01083</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>DPR-52</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>05000260</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>05/10/1967</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>06/28/1974</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>03/01/1975</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>05/04/2006</t>
         </is>
       </c>
-      <c r="R9" s="5" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S9" s="5" t="inlineStr">
+      <c r="U9" s="5" t="inlineStr">
         <is>
           <t>06/28/2034</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/bf2.html</t>
         </is>
@@ -1457,55 +1549,65 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>Limestone County</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>01083</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>DPR-68</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>05000296</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>07/31/1968</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>07/02/1976</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>03/01/1977</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t>05/04/2006</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>07/02/2036</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/bf3.html</t>
         </is>
@@ -1559,55 +1661,65 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
+          <t>Brunswick County</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>37019</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>BRRT</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>DPR-71</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>05000325</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>02/07/1970</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>09/08/1976</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>03/18/1977</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>06/26/2006</t>
         </is>
       </c>
-      <c r="R11" s="5" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S11" s="5" t="inlineStr">
+      <c r="U11" s="5" t="inlineStr">
         <is>
           <t>09/08/2036</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/bru1.html</t>
         </is>
@@ -1661,55 +1773,65 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>Brunswick County</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>37019</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>BRRT</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>DPR-62</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>05000324</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>02/07/1970</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>12/27/1974</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>11/03/1975</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t>06/26/2006</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>12/27/2034</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/bru2.html</t>
         </is>
@@ -1763,55 +1885,65 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
+          <t>Ogle County</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>17141</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>CWE</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>NPF-37</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>05000454</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>12/31/1975</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>02/14/1985</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>09/16/1985</t>
         </is>
       </c>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>11/19/2015</t>
         </is>
       </c>
-      <c r="R13" s="5" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S13" s="5" t="inlineStr">
+      <c r="U13" s="5" t="inlineStr">
         <is>
           <t>10/31/2044</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/byro1.html</t>
         </is>
@@ -1865,55 +1997,65 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>Ogle County</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>17141</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>CWE</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>NPF-66</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>05000455</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>12/31/1975</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>01/30/1987</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>08/02/1987</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="S14" s="3" t="inlineStr">
         <is>
           <t>11/19/2015</t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="T14" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>11/06/2046</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/byro2.html</t>
         </is>
@@ -1967,55 +2109,65 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
+          <t>Callaway County</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>29027</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>DANI</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>NPF-30</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>05000483</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>04/16/1976</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>10/18/1984</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>12/19/1984</t>
         </is>
       </c>
-      <c r="Q15" s="5" t="inlineStr">
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>03/06/2015</t>
         </is>
       </c>
-      <c r="R15" s="5" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S15" s="5" t="inlineStr">
+      <c r="U15" s="5" t="inlineStr">
         <is>
           <t>10/18/2044</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/call.html</t>
         </is>
@@ -2069,55 +2221,65 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>Calvert County</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>24009</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>DPR-53</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>05000317</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>07/07/1969</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>07/31/1974</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>05/08/1975</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
+      <c r="S16" s="3" t="inlineStr">
         <is>
           <t>03/23/2000</t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr">
+      <c r="T16" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>07/31/2034</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/calv1.html</t>
         </is>
@@ -2171,55 +2333,65 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
+          <t>Calvert County</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>24009</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>DPR-69</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>05000318</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>07/07/1969</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>08/13/1976</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>04/01/1977</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="S17" s="5" t="inlineStr">
         <is>
           <t>03/23/2000</t>
         </is>
       </c>
-      <c r="R17" s="5" t="inlineStr">
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S17" s="5" t="inlineStr">
+      <c r="U17" s="5" t="inlineStr">
         <is>
           <t>08/13/2036</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/calv2.html</t>
         </is>
@@ -2273,55 +2445,65 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>York County</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>45091</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>NPF-35</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>05000413</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>08/07/1975</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>01/17/1985</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>06/29/1985</t>
         </is>
       </c>
-      <c r="Q18" s="3" t="inlineStr">
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t>12/05/2003</t>
         </is>
       </c>
-      <c r="R18" s="3" t="inlineStr">
+      <c r="T18" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t>12/05/2043</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/cat1.html</t>
         </is>
@@ -2375,55 +2557,65 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
+          <t>York County</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>45091</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>NPF-52</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>05000414</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>08/07/1975</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>05/15/1986</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>08/19/1986</t>
         </is>
       </c>
-      <c r="Q19" s="5" t="inlineStr">
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>12/05/2003</t>
         </is>
       </c>
-      <c r="R19" s="5" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S19" s="5" t="inlineStr">
+      <c r="U19" s="5" t="inlineStr">
         <is>
           <t>12/05/2043</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/cat2.html</t>
         </is>
@@ -2477,55 +2669,65 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>DeWitt County</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>17039</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>BALD</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>NPF-62</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>05000461</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>02/24/1976</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>04/17/1987</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>11/24/1987</t>
         </is>
       </c>
-      <c r="Q20" s="3" t="inlineStr">
+      <c r="S20" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R20" s="3" t="inlineStr">
+      <c r="T20" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="U20" s="3" t="inlineStr">
         <is>
           <t>09/29/2026</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/clin.html</t>
         </is>
@@ -2579,55 +2781,65 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
+          <t>Benton County</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>53005</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
           <t>B&amp;R</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>NPF-21</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>05000397</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>03/19/1973</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>04/13/1984</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>12/13/1984</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>05/22/2012</t>
         </is>
       </c>
-      <c r="R21" s="5" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S21" s="5" t="inlineStr">
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>12/20/2043</t>
         </is>
       </c>
-      <c r="T21" s="4" t="inlineStr">
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/wash2.html</t>
         </is>
@@ -2681,55 +2893,65 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>Somervell County</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>48423</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>G&amp;H</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>BRRT</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>NPF-87</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>05000445</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="P22" s="3" t="inlineStr">
         <is>
           <t>12/19/1974</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>04/17/1990</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr">
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>07/30/2024</t>
         </is>
       </c>
-      <c r="Q22" s="3" t="inlineStr">
+      <c r="S22" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R22" s="3" t="inlineStr">
+      <c r="T22" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="U22" s="3" t="inlineStr">
         <is>
           <t>02/08/2050</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/cp1.html</t>
         </is>
@@ -2783,55 +3005,65 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
+          <t>Somervell County</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>48423</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>BRRT</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>NPF-89</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>05000446</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>12/19/1974</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>04/06/1993</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
+      <c r="R23" s="5" t="inlineStr">
         <is>
           <t>07/30/2024</t>
         </is>
       </c>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R23" s="5" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S23" s="5" t="inlineStr">
+      <c r="U23" s="5" t="inlineStr">
         <is>
           <t>02/02/2053</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr">
+      <c r="V23" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/cp2.html</t>
         </is>
@@ -2885,55 +3117,65 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>Nemaha County</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>31117</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>B&amp;R</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>B&amp;R</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>DPR-46</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t>05000298</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="P24" s="3" t="inlineStr">
         <is>
           <t>06/04/1968</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
+      <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>01/18/1974</t>
         </is>
       </c>
-      <c r="P24" s="3" t="inlineStr">
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t>07/01/1974</t>
         </is>
       </c>
-      <c r="Q24" s="3" t="inlineStr">
+      <c r="S24" s="3" t="inlineStr">
         <is>
           <t>11/29/2010</t>
         </is>
       </c>
-      <c r="R24" s="3" t="inlineStr">
+      <c r="T24" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S24" s="3" t="inlineStr">
+      <c r="U24" s="3" t="inlineStr">
         <is>
           <t>01/18/2034</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/cns.html</t>
         </is>
@@ -2987,55 +3229,65 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
+          <t>Ottawa County</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>39123</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>B&amp;W</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>NPF-3</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>05000346</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>03/24/1971</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>04/22/1977</t>
         </is>
       </c>
-      <c r="P25" s="5" t="inlineStr">
+      <c r="R25" s="5" t="inlineStr">
         <is>
           <t>07/31/1978</t>
         </is>
       </c>
-      <c r="Q25" s="5" t="inlineStr">
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>12/08/2015</t>
         </is>
       </c>
-      <c r="R25" s="5" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S25" s="5" t="inlineStr">
+      <c r="U25" s="5" t="inlineStr">
         <is>
           <t>04/22/2037</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr">
+      <c r="V25" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/davi.html</t>
         </is>
@@ -3089,55 +3341,65 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>San Luis Obispo County</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>06079</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>PG&amp;E</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>PG&amp;E</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>DPR-80</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>05000275</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>4/23/1968</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
+      <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>11/02/1984</t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t>05/07/1985</t>
         </is>
       </c>
-      <c r="Q26" s="3" t="inlineStr">
+      <c r="S26" s="3" t="inlineStr">
         <is>
           <t>Withdrawn</t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
+      <c r="T26" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="U26" s="3" t="inlineStr">
         <is>
           <t>11/02/2024</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/diab1.html</t>
         </is>
@@ -3191,55 +3453,65 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
+          <t>San Luis Obispo County</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>06079</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
           <t>PG&amp;E</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>PG&amp;E</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>DPR-82</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>05000323</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>12/09/1970</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>08/26/1985</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="R27" s="5" t="inlineStr">
         <is>
           <t>03/13/1986</t>
         </is>
       </c>
-      <c r="Q27" s="5" t="inlineStr">
+      <c r="S27" s="5" t="inlineStr">
         <is>
           <t>Withdrawn</t>
         </is>
       </c>
-      <c r="R27" s="5" t="inlineStr">
+      <c r="T27" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S27" s="5" t="inlineStr">
+      <c r="U27" s="5" t="inlineStr">
         <is>
           <t>08/26/2025</t>
         </is>
       </c>
-      <c r="T27" s="4" t="inlineStr">
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/diab2.html</t>
         </is>
@@ -3293,55 +3565,65 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>Berrien County</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>26021</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
           <t>AEP</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>AEP</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>DPR-58</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="O28" s="3" t="inlineStr">
         <is>
           <t>05000315</t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="P28" s="3" t="inlineStr">
         <is>
           <t>03/25/1969</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
+      <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>10/25/1974</t>
         </is>
       </c>
-      <c r="P28" s="3" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t>08/28/1975</t>
         </is>
       </c>
-      <c r="Q28" s="3" t="inlineStr">
+      <c r="S28" s="3" t="inlineStr">
         <is>
           <t>08/30/2005</t>
         </is>
       </c>
-      <c r="R28" s="3" t="inlineStr">
+      <c r="T28" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S28" s="3" t="inlineStr">
+      <c r="U28" s="3" t="inlineStr">
         <is>
           <t>10/25/2034</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/cook1.html</t>
         </is>
@@ -3395,55 +3677,65 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
+          <t>Berrien County</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>26021</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
           <t>AEP</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>AEP</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>DPR-74</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>05000316</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>03/25/1969</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>12/23/1977</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr">
+      <c r="R29" s="5" t="inlineStr">
         <is>
           <t>07/01/1978</t>
         </is>
       </c>
-      <c r="Q29" s="5" t="inlineStr">
+      <c r="S29" s="5" t="inlineStr">
         <is>
           <t>08/30/2005</t>
         </is>
       </c>
-      <c r="R29" s="5" t="inlineStr">
+      <c r="T29" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S29" s="5" t="inlineStr">
+      <c r="U29" s="5" t="inlineStr">
         <is>
           <t>12/23/2037</t>
         </is>
       </c>
-      <c r="T29" s="4" t="inlineStr">
+      <c r="V29" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/cook2.html</t>
         </is>
@@ -3497,55 +3789,65 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>Grundy County</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>17063</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="N30" s="3" t="inlineStr">
         <is>
           <t>DPR-19</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="O30" s="3" t="inlineStr">
         <is>
           <t>05000237</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="P30" s="3" t="inlineStr">
         <is>
           <t>01/10/1966</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
+      <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>02/20/1991A</t>
         </is>
       </c>
-      <c r="P30" s="3" t="inlineStr">
+      <c r="R30" s="3" t="inlineStr">
         <is>
           <t>06/09/1970</t>
         </is>
       </c>
-      <c r="Q30" s="3" t="inlineStr">
+      <c r="S30" s="3" t="inlineStr">
         <is>
           <t>10/28/2004</t>
         </is>
       </c>
-      <c r="R30" s="3" t="inlineStr">
+      <c r="T30" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S30" s="3" t="inlineStr">
+      <c r="U30" s="3" t="inlineStr">
         <is>
           <t>12/22/2029</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/dres2.html</t>
         </is>
@@ -3599,55 +3901,65 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
+          <t>Grundy County</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>17063</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>DPR-25</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>05000249</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="P31" s="5" t="inlineStr">
         <is>
           <t>10/14/1966</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="Q31" s="5" t="inlineStr">
         <is>
           <t>01/12/1971</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr">
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>11/16/1971</t>
         </is>
       </c>
-      <c r="Q31" s="5" t="inlineStr">
+      <c r="S31" s="5" t="inlineStr">
         <is>
           <t>10/28/2004</t>
         </is>
       </c>
-      <c r="R31" s="5" t="inlineStr">
+      <c r="T31" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S31" s="5" t="inlineStr">
+      <c r="U31" s="5" t="inlineStr">
         <is>
           <t>01/12/2031</t>
         </is>
       </c>
-      <c r="T31" s="4" t="inlineStr">
+      <c r="V31" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/dres3.html</t>
         </is>
@@ -3701,55 +4013,65 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
+          <t>Appling County</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>13001</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>GPC</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>DPR-57</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="O32" s="3" t="inlineStr">
         <is>
           <t>05000321</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
+      <c r="P32" s="3" t="inlineStr">
         <is>
           <t>09/30/1969</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
+      <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>10/13/1974</t>
         </is>
       </c>
-      <c r="P32" s="3" t="inlineStr">
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t>12/31/1975</t>
         </is>
       </c>
-      <c r="Q32" s="3" t="inlineStr">
+      <c r="S32" s="3" t="inlineStr">
         <is>
           <t>01/15/2002</t>
         </is>
       </c>
-      <c r="R32" s="3" t="inlineStr">
+      <c r="T32" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="U32" s="3" t="inlineStr">
         <is>
           <t>08/06/2034</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/hat1.html</t>
         </is>
@@ -3803,55 +4125,65 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
+          <t>Appling County</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>13001</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>GPC</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>NPF-5</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>05000366</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="P33" s="5" t="inlineStr">
         <is>
           <t>12/27/1972</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>06/13/1978</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="R33" s="5" t="inlineStr">
         <is>
           <t>09/05/1979</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="inlineStr">
+      <c r="S33" s="5" t="inlineStr">
         <is>
           <t>01/15/2002</t>
         </is>
       </c>
-      <c r="R33" s="5" t="inlineStr">
+      <c r="T33" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S33" s="5" t="inlineStr">
+      <c r="U33" s="5" t="inlineStr">
         <is>
           <t>06/13/2038</t>
         </is>
       </c>
-      <c r="T33" s="4" t="inlineStr">
+      <c r="V33" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/hat2.html</t>
         </is>
@@ -3905,55 +4237,65 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
+          <t>Monroe County</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>26115</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>DANI</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>NPF-43</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="O34" s="3" t="inlineStr">
         <is>
           <t>05000341</t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr">
+      <c r="P34" s="3" t="inlineStr">
         <is>
           <t>09/26/1972</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
+      <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>03/20/1985</t>
         </is>
       </c>
-      <c r="P34" s="3" t="inlineStr">
+      <c r="R34" s="3" t="inlineStr">
         <is>
           <t>01/23/1988</t>
         </is>
       </c>
-      <c r="Q34" s="3" t="inlineStr">
+      <c r="S34" s="3" t="inlineStr">
         <is>
           <t>12/15/2016</t>
         </is>
       </c>
-      <c r="R34" s="3" t="inlineStr">
+      <c r="T34" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S34" s="3" t="inlineStr">
+      <c r="U34" s="3" t="inlineStr">
         <is>
           <t>03/20/2045</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/ferm2.html</t>
         </is>
@@ -4007,55 +4349,65 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
+          <t>Claiborne County</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>28021</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>NPF-29</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>05000416</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="P35" s="5" t="inlineStr">
         <is>
           <t>09/04/1974</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>11/01/1984</t>
         </is>
       </c>
-      <c r="P35" s="5" t="inlineStr">
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>07/01/1985</t>
         </is>
       </c>
-      <c r="Q35" s="5" t="inlineStr">
+      <c r="S35" s="5" t="inlineStr">
         <is>
           <t>12/01/2016</t>
         </is>
       </c>
-      <c r="R35" s="5" t="inlineStr">
+      <c r="T35" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S35" s="5" t="inlineStr">
+      <c r="U35" s="5" t="inlineStr">
         <is>
           <t>11/01/2044</t>
         </is>
       </c>
-      <c r="T35" s="4" t="inlineStr">
+      <c r="V35" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/gg1.html</t>
         </is>
@@ -4109,55 +4461,65 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>Darlington County</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>45031</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>DPR-23</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="O36" s="3" t="inlineStr">
         <is>
           <t>05000261</t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="P36" s="3" t="inlineStr">
         <is>
           <t>04/13/1967</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
+      <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>07/31/1970</t>
         </is>
       </c>
-      <c r="P36" s="3" t="inlineStr">
+      <c r="R36" s="3" t="inlineStr">
         <is>
           <t>03/07/1971</t>
         </is>
       </c>
-      <c r="Q36" s="3" t="inlineStr">
+      <c r="S36" s="3" t="inlineStr">
         <is>
           <t>04/19/2004</t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr">
+      <c r="T36" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S36" s="3" t="inlineStr">
+      <c r="U36" s="3" t="inlineStr">
         <is>
           <t>07/31/2030</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/rob2.html</t>
         </is>
@@ -4211,55 +4573,65 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
+          <t>Salem County</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>34033</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>NPF-57</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>05000354</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>11/04/1974</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>07/25/1986</t>
         </is>
       </c>
-      <c r="P37" s="5" t="inlineStr">
+      <c r="R37" s="5" t="inlineStr">
         <is>
           <t>12/20/1986</t>
         </is>
       </c>
-      <c r="Q37" s="5" t="inlineStr">
+      <c r="S37" s="5" t="inlineStr">
         <is>
           <t>07/20/2011</t>
         </is>
       </c>
-      <c r="R37" s="5" t="inlineStr">
+      <c r="T37" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S37" s="5" t="inlineStr">
+      <c r="U37" s="5" t="inlineStr">
         <is>
           <t>04/11/2046</t>
         </is>
       </c>
-      <c r="T37" s="4" t="inlineStr">
+      <c r="V37" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/hope.html</t>
         </is>
@@ -4313,55 +4685,65 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>Oswego County</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>36075</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>DPR-59</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="O38" s="3" t="inlineStr">
         <is>
           <t>05000333</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr">
+      <c r="P38" s="3" t="inlineStr">
         <is>
           <t>05/20/1970</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
+      <c r="Q38" s="3" t="inlineStr">
         <is>
           <t>10/17/1974</t>
         </is>
       </c>
-      <c r="P38" s="3" t="inlineStr">
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t>07/28/1975</t>
         </is>
       </c>
-      <c r="Q38" s="3" t="inlineStr">
+      <c r="S38" s="3" t="inlineStr">
         <is>
           <t>09/08/2008</t>
         </is>
       </c>
-      <c r="R38" s="3" t="inlineStr">
+      <c r="T38" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S38" s="3" t="inlineStr">
+      <c r="U38" s="3" t="inlineStr">
         <is>
           <t>10/17/2034</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/fitz.html</t>
         </is>
@@ -4415,55 +4797,65 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
+          <t>Houston County</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>01069</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
           <t>SSI</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>DANI</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>NPF-2</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>05000348</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr">
         <is>
           <t>08/16/1972</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>06/25/1977</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="R39" s="5" t="inlineStr">
         <is>
           <t>12/01/1977</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="inlineStr">
+      <c r="S39" s="5" t="inlineStr">
         <is>
           <t>05/12/2005</t>
         </is>
       </c>
-      <c r="R39" s="5" t="inlineStr">
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S39" s="5" t="inlineStr">
+      <c r="U39" s="5" t="inlineStr">
         <is>
           <t>06/25/2037</t>
         </is>
       </c>
-      <c r="T39" s="4" t="inlineStr">
+      <c r="V39" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/far1.html</t>
         </is>
@@ -4517,55 +4909,65 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
+          <t>Houston County</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>01069</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
           <t>SSI</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="N40" s="3" t="inlineStr">
         <is>
           <t>NPF-8</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="O40" s="3" t="inlineStr">
         <is>
           <t>05000364</t>
         </is>
       </c>
-      <c r="N40" s="3" t="inlineStr">
+      <c r="P40" s="3" t="inlineStr">
         <is>
           <t>08/16/1972</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
+      <c r="Q40" s="3" t="inlineStr">
         <is>
           <t>03/31/1981</t>
         </is>
       </c>
-      <c r="P40" s="3" t="inlineStr">
+      <c r="R40" s="3" t="inlineStr">
         <is>
           <t>07/30/1981</t>
         </is>
       </c>
-      <c r="Q40" s="3" t="inlineStr">
+      <c r="S40" s="3" t="inlineStr">
         <is>
           <t>05/12/2005</t>
         </is>
       </c>
-      <c r="R40" s="3" t="inlineStr">
+      <c r="T40" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S40" s="3" t="inlineStr">
+      <c r="U40" s="3" t="inlineStr">
         <is>
           <t>03/31/2041</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/far2.html</t>
         </is>
@@ -4619,55 +5021,65 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
+          <t>LaSalle County</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>17099</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>CWE</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>NPF-11</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>05000373</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="P41" s="5" t="inlineStr">
         <is>
           <t>09/10/1973</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>04/17/1982</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="R41" s="5" t="inlineStr">
         <is>
           <t>01/01/1984</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="inlineStr">
+      <c r="S41" s="5" t="inlineStr">
         <is>
           <t>10/19/2016</t>
         </is>
       </c>
-      <c r="R41" s="5" t="inlineStr">
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S41" s="5" t="inlineStr">
+      <c r="U41" s="5" t="inlineStr">
         <is>
           <t>04/17/2042</t>
         </is>
       </c>
-      <c r="T41" s="4" t="inlineStr">
+      <c r="V41" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/lasa1.html</t>
         </is>
@@ -4721,55 +5133,65 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t>LaSalle County</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>17099</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>CWE</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="N42" s="3" t="inlineStr">
         <is>
           <t>NPF-18</t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
+      <c r="O42" s="3" t="inlineStr">
         <is>
           <t>05000374</t>
         </is>
       </c>
-      <c r="N42" s="3" t="inlineStr">
+      <c r="P42" s="3" t="inlineStr">
         <is>
           <t>09/10/1973</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
+      <c r="Q42" s="3" t="inlineStr">
         <is>
           <t>12/16/1983</t>
         </is>
       </c>
-      <c r="P42" s="3" t="inlineStr">
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t>10/19/1984</t>
         </is>
       </c>
-      <c r="Q42" s="3" t="inlineStr">
+      <c r="S42" s="3" t="inlineStr">
         <is>
           <t>10/19/2016</t>
         </is>
       </c>
-      <c r="R42" s="3" t="inlineStr">
+      <c r="T42" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t>12/16/2043</t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/lasa2.html</t>
         </is>
@@ -4823,55 +5245,65 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
+          <t>Montgomery County</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>42091</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>NPF-39</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>05000352</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>06/19/1974</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>08/08/1985</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr">
+      <c r="R43" s="5" t="inlineStr">
         <is>
           <t>02/01/1986</t>
         </is>
       </c>
-      <c r="Q43" s="5" t="inlineStr">
+      <c r="S43" s="5" t="inlineStr">
         <is>
           <t>10/20/2014</t>
         </is>
       </c>
-      <c r="R43" s="5" t="inlineStr">
+      <c r="T43" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S43" s="5" t="inlineStr">
+      <c r="U43" s="5" t="inlineStr">
         <is>
           <t>10/26/2044</t>
         </is>
       </c>
-      <c r="T43" s="4" t="inlineStr">
+      <c r="V43" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/lim1.html</t>
         </is>
@@ -4925,55 +5357,65 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>Montgomery County</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>42091</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="N44" s="3" t="inlineStr">
         <is>
           <t>NPF-85</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="O44" s="3" t="inlineStr">
         <is>
           <t>05000353</t>
         </is>
       </c>
-      <c r="N44" s="3" t="inlineStr">
+      <c r="P44" s="3" t="inlineStr">
         <is>
           <t>06/19/1974</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
+      <c r="Q44" s="3" t="inlineStr">
         <is>
           <t>08/25/1989</t>
         </is>
       </c>
-      <c r="P44" s="3" t="inlineStr">
+      <c r="R44" s="3" t="inlineStr">
         <is>
           <t>01/08/1990</t>
         </is>
       </c>
-      <c r="Q44" s="3" t="inlineStr">
+      <c r="S44" s="3" t="inlineStr">
         <is>
           <t>10/20/2014</t>
         </is>
       </c>
-      <c r="R44" s="3" t="inlineStr">
+      <c r="T44" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S44" s="3" t="inlineStr">
+      <c r="U44" s="3" t="inlineStr">
         <is>
           <t>06/22/2049</t>
         </is>
       </c>
-      <c r="T44" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/lim2.html</t>
         </is>
@@ -5027,55 +5469,65 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
+          <t>Mecklenburg County</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>37119</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>NPF-9</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>05000369</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>02/23/1973</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>05/27/1981</t>
         </is>
       </c>
-      <c r="P45" s="5" t="inlineStr">
+      <c r="R45" s="5" t="inlineStr">
         <is>
           <t>12/01/1981</t>
         </is>
       </c>
-      <c r="Q45" s="5" t="inlineStr">
+      <c r="S45" s="5" t="inlineStr">
         <is>
           <t>12/05/2003</t>
         </is>
       </c>
-      <c r="R45" s="5" t="inlineStr">
+      <c r="T45" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S45" s="5" t="inlineStr">
+      <c r="U45" s="5" t="inlineStr">
         <is>
           <t>06/12/204</t>
         </is>
       </c>
-      <c r="T45" s="4" t="inlineStr">
+      <c r="V45" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/mcg1.html</t>
         </is>
@@ -5129,55 +5581,65 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
+          <t>Mecklenburg County</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>37119</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="N46" s="3" t="inlineStr">
         <is>
           <t>NPF-17</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
+      <c r="O46" s="3" t="inlineStr">
         <is>
           <t>05000370</t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr">
+      <c r="P46" s="3" t="inlineStr">
         <is>
           <t>02/23/1973</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
+      <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>05/27/1983</t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
+      <c r="R46" s="3" t="inlineStr">
         <is>
           <t>03/01/1984</t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
+      <c r="S46" s="3" t="inlineStr">
         <is>
           <t>12/05/2003</t>
         </is>
       </c>
-      <c r="R46" s="3" t="inlineStr">
+      <c r="T46" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S46" s="3" t="inlineStr">
+      <c r="U46" s="3" t="inlineStr">
         <is>
           <t>03/03/2043</t>
         </is>
       </c>
-      <c r="T46" s="2" t="inlineStr">
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/mcg2.html</t>
         </is>
@@ -5231,55 +5693,65 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
+          <t>New London County</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>09011</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>DPR-65</t>
         </is>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>05000336</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>12/11/1970</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>09/26/1975</t>
         </is>
       </c>
-      <c r="P47" s="5" t="inlineStr">
+      <c r="R47" s="5" t="inlineStr">
         <is>
           <t>12/26/1975</t>
         </is>
       </c>
-      <c r="Q47" s="5" t="inlineStr">
+      <c r="S47" s="5" t="inlineStr">
         <is>
           <t>11/28/2005</t>
         </is>
       </c>
-      <c r="R47" s="5" t="inlineStr">
+      <c r="T47" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S47" s="5" t="inlineStr">
+      <c r="U47" s="5" t="inlineStr">
         <is>
           <t>07/31/2035</t>
         </is>
       </c>
-      <c r="T47" s="4" t="inlineStr">
+      <c r="V47" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/mill2.html</t>
         </is>
@@ -5333,55 +5805,65 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
+          <t>New London County</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>09011</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="N48" s="3" t="inlineStr">
         <is>
           <t>NPF-49</t>
         </is>
       </c>
-      <c r="M48" s="3" t="inlineStr">
+      <c r="O48" s="3" t="inlineStr">
         <is>
           <t>05000423</t>
         </is>
       </c>
-      <c r="N48" s="3" t="inlineStr">
+      <c r="P48" s="3" t="inlineStr">
         <is>
           <t>08/09/1974</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
+      <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>01/31/1986</t>
         </is>
       </c>
-      <c r="P48" s="3" t="inlineStr">
+      <c r="R48" s="3" t="inlineStr">
         <is>
           <t>04/23/1986</t>
         </is>
       </c>
-      <c r="Q48" s="3" t="inlineStr">
+      <c r="S48" s="3" t="inlineStr">
         <is>
           <t>11/28/2005</t>
         </is>
       </c>
-      <c r="R48" s="3" t="inlineStr">
+      <c r="T48" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S48" s="3" t="inlineStr">
+      <c r="U48" s="3" t="inlineStr">
         <is>
           <t>11/25/2045</t>
         </is>
       </c>
-      <c r="T48" s="2" t="inlineStr">
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/mill3.html</t>
         </is>
@@ -5435,55 +5917,65 @@
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
+          <t>Wright County</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>27171</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr">
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>DPR-22</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>05000263</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="P49" s="5" t="inlineStr">
         <is>
           <t>06/19/1967</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>01/09/1981B</t>
         </is>
       </c>
-      <c r="P49" s="5" t="inlineStr">
+      <c r="R49" s="5" t="inlineStr">
         <is>
           <t>06/30/1971</t>
         </is>
       </c>
-      <c r="Q49" s="5" t="inlineStr">
+      <c r="S49" s="5" t="inlineStr">
         <is>
           <t>11/08/2006</t>
         </is>
       </c>
-      <c r="R49" s="5" t="inlineStr">
+      <c r="T49" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S49" s="5" t="inlineStr">
+      <c r="U49" s="5" t="inlineStr">
         <is>
           <t>09/08/2030</t>
         </is>
       </c>
-      <c r="T49" s="4" t="inlineStr">
+      <c r="V49" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/mont.html</t>
         </is>
@@ -5537,55 +6029,65 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
+          <t>Oswego County</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>36075</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
           <t>NIAG</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>DPR-63</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="O50" s="3" t="inlineStr">
         <is>
           <t>05000220</t>
         </is>
       </c>
-      <c r="N50" s="3" t="inlineStr">
+      <c r="P50" s="3" t="inlineStr">
         <is>
           <t>04/12/1965</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
+      <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>12/26/1974C</t>
         </is>
       </c>
-      <c r="P50" s="3" t="inlineStr">
+      <c r="R50" s="3" t="inlineStr">
         <is>
           <t>12/01/1969</t>
         </is>
       </c>
-      <c r="Q50" s="3" t="inlineStr">
+      <c r="S50" s="3" t="inlineStr">
         <is>
           <t>10/31/2006</t>
         </is>
       </c>
-      <c r="R50" s="3" t="inlineStr">
+      <c r="T50" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S50" s="3" t="inlineStr">
+      <c r="U50" s="3" t="inlineStr">
         <is>
           <t>08/22/2029</t>
         </is>
       </c>
-      <c r="T50" s="2" t="inlineStr">
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/nmp1.html</t>
         </is>
@@ -5639,55 +6141,65 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
+          <t>Oswego County</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>36075</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>NPF-69</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>05000410</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="P51" s="5" t="inlineStr">
         <is>
           <t>06/24/1974</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>07/02/1987</t>
         </is>
       </c>
-      <c r="P51" s="5" t="inlineStr">
+      <c r="R51" s="5" t="inlineStr">
         <is>
           <t>03/11/1988</t>
         </is>
       </c>
-      <c r="Q51" s="5" t="inlineStr">
+      <c r="S51" s="5" t="inlineStr">
         <is>
           <t>10/31/2006</t>
         </is>
       </c>
-      <c r="R51" s="5" t="inlineStr">
+      <c r="T51" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S51" s="5" t="inlineStr">
+      <c r="U51" s="5" t="inlineStr">
         <is>
           <t>10/31/2046</t>
         </is>
       </c>
-      <c r="T51" s="4" t="inlineStr">
+      <c r="V51" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/nmp2.html</t>
         </is>
@@ -5741,55 +6253,65 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
+          <t>Louisa County</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>51109</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="N52" s="3" t="inlineStr">
         <is>
           <t>NPF-4</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="O52" s="3" t="inlineStr">
         <is>
           <t>05000338</t>
         </is>
       </c>
-      <c r="N52" s="3" t="inlineStr">
+      <c r="P52" s="3" t="inlineStr">
         <is>
           <t>02/19/1971</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
+      <c r="Q52" s="3" t="inlineStr">
         <is>
           <t>04/01/1978</t>
         </is>
       </c>
-      <c r="P52" s="3" t="inlineStr">
+      <c r="R52" s="3" t="inlineStr">
         <is>
           <t>06/06/1978</t>
         </is>
       </c>
-      <c r="Q52" s="3" t="inlineStr">
+      <c r="S52" s="3" t="inlineStr">
         <is>
           <t>03/20/2003</t>
         </is>
       </c>
-      <c r="R52" s="3" t="inlineStr">
+      <c r="T52" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S52" s="3" t="inlineStr">
+      <c r="U52" s="3" t="inlineStr">
         <is>
           <t>04/01/2038</t>
         </is>
       </c>
-      <c r="T52" s="2" t="inlineStr">
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/na1.html</t>
         </is>
@@ -5843,55 +6365,65 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
+          <t>Louisa County</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>51109</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr">
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>NPF-7</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>05000339</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="P53" s="5" t="inlineStr">
         <is>
           <t>02/19/1971</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>08/21/1980</t>
         </is>
       </c>
-      <c r="P53" s="5" t="inlineStr">
+      <c r="R53" s="5" t="inlineStr">
         <is>
           <t>12/14/1980</t>
         </is>
       </c>
-      <c r="Q53" s="5" t="inlineStr">
+      <c r="S53" s="5" t="inlineStr">
         <is>
           <t>03/20/2003</t>
         </is>
       </c>
-      <c r="R53" s="5" t="inlineStr">
+      <c r="T53" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S53" s="5" t="inlineStr">
+      <c r="U53" s="5" t="inlineStr">
         <is>
           <t>08/21/2040</t>
         </is>
       </c>
-      <c r="T53" s="4" t="inlineStr">
+      <c r="V53" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/na2.html</t>
         </is>
@@ -5945,55 +6477,65 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
+          <t>Oconee County</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>45073</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
           <t>DBDB</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="N54" s="3" t="inlineStr">
         <is>
           <t>DPR-38</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="O54" s="3" t="inlineStr">
         <is>
           <t>05000269</t>
         </is>
       </c>
-      <c r="N54" s="3" t="inlineStr">
+      <c r="P54" s="3" t="inlineStr">
         <is>
           <t>11/06/1967</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
+      <c r="Q54" s="3" t="inlineStr">
         <is>
           <t>02/06/1973</t>
         </is>
       </c>
-      <c r="P54" s="3" t="inlineStr">
+      <c r="R54" s="3" t="inlineStr">
         <is>
           <t>07/15/1973</t>
         </is>
       </c>
-      <c r="Q54" s="3" t="inlineStr">
+      <c r="S54" s="3" t="inlineStr">
         <is>
           <t>05/23/2000</t>
         </is>
       </c>
-      <c r="R54" s="3" t="inlineStr">
+      <c r="T54" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S54" s="3" t="inlineStr">
+      <c r="U54" s="3" t="inlineStr">
         <is>
           <t>02/06/2033</t>
         </is>
       </c>
-      <c r="T54" s="2" t="inlineStr">
+      <c r="V54" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/oco1.html</t>
         </is>
@@ -6047,55 +6589,65 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
+          <t>Oconee County</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>45073</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
           <t>DBDB</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
+      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>DPR-47</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>05000270</t>
         </is>
       </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="P55" s="5" t="inlineStr">
         <is>
           <t>11/06/1967</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>10/06/1973</t>
         </is>
       </c>
-      <c r="P55" s="5" t="inlineStr">
+      <c r="R55" s="5" t="inlineStr">
         <is>
           <t>09/09/1974</t>
         </is>
       </c>
-      <c r="Q55" s="5" t="inlineStr">
+      <c r="S55" s="5" t="inlineStr">
         <is>
           <t>05/23/2000</t>
         </is>
       </c>
-      <c r="R55" s="5" t="inlineStr">
+      <c r="T55" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S55" s="5" t="inlineStr">
+      <c r="U55" s="5" t="inlineStr">
         <is>
           <t>10/06/2033</t>
         </is>
       </c>
-      <c r="T55" s="4" t="inlineStr">
+      <c r="V55" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/oco2.html</t>
         </is>
@@ -6149,55 +6701,65 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>Oconee County</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>45073</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
           <t>DBDB</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>DUKE</t>
         </is>
       </c>
-      <c r="L56" s="3" t="inlineStr">
+      <c r="N56" s="3" t="inlineStr">
         <is>
           <t>DPR-55</t>
         </is>
       </c>
-      <c r="M56" s="3" t="inlineStr">
+      <c r="O56" s="3" t="inlineStr">
         <is>
           <t>05000287</t>
         </is>
       </c>
-      <c r="N56" s="3" t="inlineStr">
+      <c r="P56" s="3" t="inlineStr">
         <is>
           <t>11/06/1967</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
+      <c r="Q56" s="3" t="inlineStr">
         <is>
           <t>07/19/1974</t>
         </is>
       </c>
-      <c r="P56" s="3" t="inlineStr">
+      <c r="R56" s="3" t="inlineStr">
         <is>
           <t>12/16/1974</t>
         </is>
       </c>
-      <c r="Q56" s="3" t="inlineStr">
+      <c r="S56" s="3" t="inlineStr">
         <is>
           <t>05/23/2000</t>
         </is>
       </c>
-      <c r="R56" s="3" t="inlineStr">
+      <c r="T56" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S56" s="3" t="inlineStr">
+      <c r="U56" s="3" t="inlineStr">
         <is>
           <t>07/19/2034</t>
         </is>
       </c>
-      <c r="T56" s="2" t="inlineStr">
+      <c r="V56" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/oco3.html</t>
         </is>
@@ -6251,55 +6813,65 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
+          <t>Maricopa County</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>04013</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr">
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>NPF-41</t>
         </is>
       </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>05000528</t>
         </is>
       </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="P57" s="5" t="inlineStr">
         <is>
           <t>05/25/1976</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>06/01/1985</t>
         </is>
       </c>
-      <c r="P57" s="5" t="inlineStr">
+      <c r="R57" s="5" t="inlineStr">
         <is>
           <t>01/28/1986</t>
         </is>
       </c>
-      <c r="Q57" s="5" t="inlineStr">
+      <c r="S57" s="5" t="inlineStr">
         <is>
           <t>04/21/2011</t>
         </is>
       </c>
-      <c r="R57" s="5" t="inlineStr">
+      <c r="T57" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S57" s="5" t="inlineStr">
+      <c r="U57" s="5" t="inlineStr">
         <is>
           <t>06/01/2045</t>
         </is>
       </c>
-      <c r="T57" s="4" t="inlineStr">
+      <c r="V57" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/palo1.html</t>
         </is>
@@ -6353,55 +6925,65 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
+          <t>Maricopa County</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>04013</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L58" s="3" t="inlineStr">
+      <c r="N58" s="3" t="inlineStr">
         <is>
           <t>NPF-51</t>
         </is>
       </c>
-      <c r="M58" s="3" t="inlineStr">
+      <c r="O58" s="3" t="inlineStr">
         <is>
           <t>05000529</t>
         </is>
       </c>
-      <c r="N58" s="3" t="inlineStr">
+      <c r="P58" s="3" t="inlineStr">
         <is>
           <t>05/25/1976</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
+      <c r="Q58" s="3" t="inlineStr">
         <is>
           <t>04/24/1986</t>
         </is>
       </c>
-      <c r="P58" s="3" t="inlineStr">
+      <c r="R58" s="3" t="inlineStr">
         <is>
           <t>09/19/1986</t>
         </is>
       </c>
-      <c r="Q58" s="3" t="inlineStr">
+      <c r="S58" s="3" t="inlineStr">
         <is>
           <t>04/21/2011</t>
         </is>
       </c>
-      <c r="R58" s="3" t="inlineStr">
+      <c r="T58" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S58" s="3" t="inlineStr">
+      <c r="U58" s="3" t="inlineStr">
         <is>
           <t>04/24/2046</t>
         </is>
       </c>
-      <c r="T58" s="2" t="inlineStr">
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/palo2.html</t>
         </is>
@@ -6455,55 +7037,65 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
+          <t>Maricopa County</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>04013</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="M59" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>NPF-74</t>
         </is>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>05000530</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="P59" s="5" t="inlineStr">
         <is>
           <t>05/25/1976</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>11/25/1987</t>
         </is>
       </c>
-      <c r="P59" s="5" t="inlineStr">
+      <c r="R59" s="5" t="inlineStr">
         <is>
           <t>01/08/1988</t>
         </is>
       </c>
-      <c r="Q59" s="5" t="inlineStr">
+      <c r="S59" s="5" t="inlineStr">
         <is>
           <t>04/21/2011</t>
         </is>
       </c>
-      <c r="R59" s="5" t="inlineStr">
+      <c r="T59" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S59" s="5" t="inlineStr">
+      <c r="U59" s="5" t="inlineStr">
         <is>
           <t>11/25/2047</t>
         </is>
       </c>
-      <c r="T59" s="4" t="inlineStr">
+      <c r="V59" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/palo3.html</t>
         </is>
@@ -6557,55 +7149,65 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
+          <t>York County</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>42133</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="N60" s="3" t="inlineStr">
         <is>
           <t>DPR-44</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
+      <c r="O60" s="3" t="inlineStr">
         <is>
           <t>05000277</t>
         </is>
       </c>
-      <c r="N60" s="3" t="inlineStr">
+      <c r="P60" s="3" t="inlineStr">
         <is>
           <t>01/31/1968</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
+      <c r="Q60" s="3" t="inlineStr">
         <is>
           <t>10/25/1973</t>
         </is>
       </c>
-      <c r="P60" s="3" t="inlineStr">
+      <c r="R60" s="3" t="inlineStr">
         <is>
           <t>07/05/1974</t>
         </is>
       </c>
-      <c r="Q60" s="3" t="inlineStr">
+      <c r="S60" s="3" t="inlineStr">
         <is>
           <t>05/07/2003</t>
         </is>
       </c>
-      <c r="R60" s="3" t="inlineStr">
+      <c r="T60" s="3" t="inlineStr">
         <is>
           <t>03/05/2020</t>
         </is>
       </c>
-      <c r="S60" s="3" t="inlineStr">
+      <c r="U60" s="3" t="inlineStr">
         <is>
           <t>08/08/2033</t>
         </is>
       </c>
-      <c r="T60" s="2" t="inlineStr">
+      <c r="V60" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/pb2.html</t>
         </is>
@@ -6659,55 +7261,65 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
+          <t>York County</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>42133</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>DPR-56</t>
         </is>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>05000278</t>
         </is>
       </c>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="P61" s="5" t="inlineStr">
         <is>
           <t>01/31/1968</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>07/02/1974</t>
         </is>
       </c>
-      <c r="P61" s="5" t="inlineStr">
+      <c r="R61" s="5" t="inlineStr">
         <is>
           <t>12/23/1974</t>
         </is>
       </c>
-      <c r="Q61" s="5" t="inlineStr">
+      <c r="S61" s="5" t="inlineStr">
         <is>
           <t>05/07/2003</t>
         </is>
       </c>
-      <c r="R61" s="5" t="inlineStr">
+      <c r="T61" s="5" t="inlineStr">
         <is>
           <t>03/05/2020</t>
         </is>
       </c>
-      <c r="S61" s="5" t="inlineStr">
+      <c r="U61" s="5" t="inlineStr">
         <is>
           <t>07/02/2034</t>
         </is>
       </c>
-      <c r="T61" s="4" t="inlineStr">
+      <c r="V61" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/pb3.html</t>
         </is>
@@ -6761,55 +7373,65 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
+          <t>Lake County</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>39085</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
           <t>GIL</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>KAIS</t>
         </is>
       </c>
-      <c r="L62" s="3" t="inlineStr">
+      <c r="N62" s="3" t="inlineStr">
         <is>
           <t>NPF-58</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr">
+      <c r="O62" s="3" t="inlineStr">
         <is>
           <t>05000440</t>
         </is>
       </c>
-      <c r="N62" s="3" t="inlineStr">
+      <c r="P62" s="3" t="inlineStr">
         <is>
           <t>05/03/1977</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
+      <c r="Q62" s="3" t="inlineStr">
         <is>
           <t>11/13/1986</t>
         </is>
       </c>
-      <c r="P62" s="3" t="inlineStr">
+      <c r="R62" s="3" t="inlineStr">
         <is>
           <t>11/18/1987</t>
         </is>
       </c>
-      <c r="Q62" s="3" t="inlineStr">
+      <c r="S62" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R62" s="3" t="inlineStr">
+      <c r="T62" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S62" s="3" t="inlineStr">
+      <c r="U62" s="3" t="inlineStr">
         <is>
           <t>03/18/2026</t>
         </is>
       </c>
-      <c r="T62" s="2" t="inlineStr">
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/perr1.html</t>
         </is>
@@ -6863,55 +7485,65 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
+          <t>Manitowoc County</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>55071</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>DPR-24</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="O63" s="5" t="inlineStr">
         <is>
           <t>05000266</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="P63" s="5" t="inlineStr">
         <is>
           <t>07/19/1967</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="Q63" s="5" t="inlineStr">
         <is>
           <t>10/05/1970</t>
         </is>
       </c>
-      <c r="P63" s="5" t="inlineStr">
+      <c r="R63" s="5" t="inlineStr">
         <is>
           <t>12/21/1970</t>
         </is>
       </c>
-      <c r="Q63" s="5" t="inlineStr">
+      <c r="S63" s="5" t="inlineStr">
         <is>
           <t>12/22/2005</t>
         </is>
       </c>
-      <c r="R63" s="5" t="inlineStr">
+      <c r="T63" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S63" s="5" t="inlineStr">
+      <c r="U63" s="5" t="inlineStr">
         <is>
           <t>10/05/2030</t>
         </is>
       </c>
-      <c r="T63" s="4" t="inlineStr">
+      <c r="V63" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/poin1.html</t>
         </is>
@@ -6965,55 +7597,65 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
+          <t>Manitowoc County</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>55071</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L64" s="3" t="inlineStr">
+      <c r="N64" s="3" t="inlineStr">
         <is>
           <t>DPR-27</t>
         </is>
       </c>
-      <c r="M64" s="3" t="inlineStr">
+      <c r="O64" s="3" t="inlineStr">
         <is>
           <t>05000301</t>
         </is>
       </c>
-      <c r="N64" s="3" t="inlineStr">
+      <c r="P64" s="3" t="inlineStr">
         <is>
           <t>07/25/1968</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
+      <c r="Q64" s="3" t="inlineStr">
         <is>
           <t>03/08/1973D</t>
         </is>
       </c>
-      <c r="P64" s="3" t="inlineStr">
+      <c r="R64" s="3" t="inlineStr">
         <is>
           <t>10/01/1972</t>
         </is>
       </c>
-      <c r="Q64" s="3" t="inlineStr">
+      <c r="S64" s="3" t="inlineStr">
         <is>
           <t>12/22/2005</t>
         </is>
       </c>
-      <c r="R64" s="3" t="inlineStr">
+      <c r="T64" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S64" s="3" t="inlineStr">
+      <c r="U64" s="3" t="inlineStr">
         <is>
           <t>03/08/2033</t>
         </is>
       </c>
-      <c r="T64" s="2" t="inlineStr">
+      <c r="V64" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/poin2.html</t>
         </is>
@@ -7067,55 +7709,65 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
+          <t>Goodhue County</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>27049</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
           <t>FLUR</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
+      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>NSP</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>DPR-42</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>05000282</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="P65" s="5" t="inlineStr">
         <is>
           <t>06/25/1968</t>
         </is>
       </c>
-      <c r="O65" s="5" t="inlineStr">
+      <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>04/05/1974E</t>
         </is>
       </c>
-      <c r="P65" s="5" t="inlineStr">
+      <c r="R65" s="5" t="inlineStr">
         <is>
           <t>12/16/1973</t>
         </is>
       </c>
-      <c r="Q65" s="5" t="inlineStr">
+      <c r="S65" s="5" t="inlineStr">
         <is>
           <t>06/27/2011</t>
         </is>
       </c>
-      <c r="R65" s="5" t="inlineStr">
+      <c r="T65" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S65" s="5" t="inlineStr">
+      <c r="U65" s="5" t="inlineStr">
         <is>
           <t>08/09/2033</t>
         </is>
       </c>
-      <c r="T65" s="4" t="inlineStr">
+      <c r="V65" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/prai1.html</t>
         </is>
@@ -7169,55 +7821,65 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
+          <t>Goodhue County</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>27049</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
           <t>FLUR</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>NSP</t>
         </is>
       </c>
-      <c r="L66" s="3" t="inlineStr">
+      <c r="N66" s="3" t="inlineStr">
         <is>
           <t>DPR-60</t>
         </is>
       </c>
-      <c r="M66" s="3" t="inlineStr">
+      <c r="O66" s="3" t="inlineStr">
         <is>
           <t>05000306</t>
         </is>
       </c>
-      <c r="N66" s="3" t="inlineStr">
+      <c r="P66" s="3" t="inlineStr">
         <is>
           <t>06/25/1968</t>
         </is>
       </c>
-      <c r="O66" s="3" t="inlineStr">
+      <c r="Q66" s="3" t="inlineStr">
         <is>
           <t>10/29/1974</t>
         </is>
       </c>
-      <c r="P66" s="3" t="inlineStr">
+      <c r="R66" s="3" t="inlineStr">
         <is>
           <t>12/21/1974</t>
         </is>
       </c>
-      <c r="Q66" s="3" t="inlineStr">
+      <c r="S66" s="3" t="inlineStr">
         <is>
           <t>06/27/2011</t>
         </is>
       </c>
-      <c r="R66" s="3" t="inlineStr">
+      <c r="T66" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S66" s="3" t="inlineStr">
+      <c r="U66" s="3" t="inlineStr">
         <is>
           <t>10/29/2034</t>
         </is>
       </c>
-      <c r="T66" s="2" t="inlineStr">
+      <c r="V66" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/prai2.html</t>
         </is>
@@ -7271,55 +7933,65 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
+          <t>Rock Island County</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>17161</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr">
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="L67" s="5" t="inlineStr">
+      <c r="N67" s="5" t="inlineStr">
         <is>
           <t>DPR-29</t>
         </is>
       </c>
-      <c r="M67" s="5" t="inlineStr">
+      <c r="O67" s="5" t="inlineStr">
         <is>
           <t>05000254</t>
         </is>
       </c>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="P67" s="5" t="inlineStr">
         <is>
           <t>02/15/1967</t>
         </is>
       </c>
-      <c r="O67" s="5" t="inlineStr">
+      <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>12/14/1972</t>
         </is>
       </c>
-      <c r="P67" s="5" t="inlineStr">
+      <c r="R67" s="5" t="inlineStr">
         <is>
           <t>02/18/1973</t>
         </is>
       </c>
-      <c r="Q67" s="5" t="inlineStr">
+      <c r="S67" s="5" t="inlineStr">
         <is>
           <t>10/28/2004</t>
         </is>
       </c>
-      <c r="R67" s="5" t="inlineStr">
+      <c r="T67" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S67" s="5" t="inlineStr">
+      <c r="U67" s="5" t="inlineStr">
         <is>
           <t>12/14/2032</t>
         </is>
       </c>
-      <c r="T67" s="4" t="inlineStr">
+      <c r="V67" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/quad1.html</t>
         </is>
@@ -7373,55 +8045,65 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
+          <t>Rock Island County</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>17161</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
           <t>S&amp;L</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="L68" s="3" t="inlineStr">
+      <c r="N68" s="3" t="inlineStr">
         <is>
           <t>DPR-30</t>
         </is>
       </c>
-      <c r="M68" s="3" t="inlineStr">
+      <c r="O68" s="3" t="inlineStr">
         <is>
           <t>05000265</t>
         </is>
       </c>
-      <c r="N68" s="3" t="inlineStr">
+      <c r="P68" s="3" t="inlineStr">
         <is>
           <t>02/15/1967</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
+      <c r="Q68" s="3" t="inlineStr">
         <is>
           <t>12/14/1972</t>
         </is>
       </c>
-      <c r="P68" s="3" t="inlineStr">
+      <c r="R68" s="3" t="inlineStr">
         <is>
           <t>03/10/1973</t>
         </is>
       </c>
-      <c r="Q68" s="3" t="inlineStr">
+      <c r="S68" s="3" t="inlineStr">
         <is>
           <t>10/28/2004</t>
         </is>
       </c>
-      <c r="R68" s="3" t="inlineStr">
+      <c r="T68" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S68" s="3" t="inlineStr">
+      <c r="U68" s="3" t="inlineStr">
         <is>
           <t>12/14/2032</t>
         </is>
       </c>
-      <c r="T68" s="2" t="inlineStr">
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/quad2.html</t>
         </is>
@@ -7475,55 +8157,65 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
+          <t>Wayne County</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>36117</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
           <t>GIL</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr">
+      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L69" s="5" t="inlineStr">
+      <c r="N69" s="5" t="inlineStr">
         <is>
           <t>DPR-18</t>
         </is>
       </c>
-      <c r="M69" s="5" t="inlineStr">
+      <c r="O69" s="5" t="inlineStr">
         <is>
           <t>05000244</t>
         </is>
       </c>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="P69" s="5" t="inlineStr">
         <is>
           <t>04/25/1966</t>
         </is>
       </c>
-      <c r="O69" s="5" t="inlineStr">
+      <c r="Q69" s="5" t="inlineStr">
         <is>
           <t>09/19/1969</t>
         </is>
       </c>
-      <c r="P69" s="5" t="inlineStr">
+      <c r="R69" s="5" t="inlineStr">
         <is>
           <t>07/01/1970</t>
         </is>
       </c>
-      <c r="Q69" s="5" t="inlineStr">
+      <c r="S69" s="5" t="inlineStr">
         <is>
           <t>05/19/2004</t>
         </is>
       </c>
-      <c r="R69" s="5" t="inlineStr">
+      <c r="T69" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S69" s="5" t="inlineStr">
+      <c r="U69" s="5" t="inlineStr">
         <is>
           <t>09/18/2029</t>
         </is>
       </c>
-      <c r="T69" s="4" t="inlineStr">
+      <c r="V69" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/ginn.html</t>
         </is>
@@ -7577,55 +8269,65 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
+          <t>West Feliciana Parish</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L70" s="3" t="inlineStr">
+      <c r="N70" s="3" t="inlineStr">
         <is>
           <t>NPF-47</t>
         </is>
       </c>
-      <c r="M70" s="3" t="inlineStr">
+      <c r="O70" s="3" t="inlineStr">
         <is>
           <t>05000458</t>
         </is>
       </c>
-      <c r="N70" s="3" t="inlineStr">
+      <c r="P70" s="3" t="inlineStr">
         <is>
           <t>03/25/1977</t>
         </is>
       </c>
-      <c r="O70" s="3" t="inlineStr">
+      <c r="Q70" s="3" t="inlineStr">
         <is>
           <t>11/20/1985</t>
         </is>
       </c>
-      <c r="P70" s="3" t="inlineStr">
+      <c r="R70" s="3" t="inlineStr">
         <is>
           <t>06/16/1986</t>
         </is>
       </c>
-      <c r="Q70" s="3" t="inlineStr">
+      <c r="S70" s="3" t="inlineStr">
         <is>
           <t>12/20/2018</t>
         </is>
       </c>
-      <c r="R70" s="3" t="inlineStr">
+      <c r="T70" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S70" s="3" t="inlineStr">
+      <c r="U70" s="3" t="inlineStr">
         <is>
           <t>08/29/2045</t>
         </is>
       </c>
-      <c r="T70" s="2" t="inlineStr">
+      <c r="V70" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/rbs1.html</t>
         </is>
@@ -7679,55 +8381,65 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
+          <t>St. Lucie County</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>12111</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="K71" s="4" t="inlineStr">
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="N71" s="5" t="inlineStr">
         <is>
           <t>DPR-67</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="O71" s="5" t="inlineStr">
         <is>
           <t>05000335</t>
         </is>
       </c>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="P71" s="5" t="inlineStr">
         <is>
           <t>07/01/1970</t>
         </is>
       </c>
-      <c r="O71" s="5" t="inlineStr">
+      <c r="Q71" s="5" t="inlineStr">
         <is>
           <t>03/01/1976</t>
         </is>
       </c>
-      <c r="P71" s="5" t="inlineStr">
+      <c r="R71" s="5" t="inlineStr">
         <is>
           <t>12/21/1976</t>
         </is>
       </c>
-      <c r="Q71" s="5" t="inlineStr">
+      <c r="S71" s="5" t="inlineStr">
         <is>
           <t>10/02/2003</t>
         </is>
       </c>
-      <c r="R71" s="5" t="inlineStr">
+      <c r="T71" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S71" s="5" t="inlineStr">
+      <c r="U71" s="5" t="inlineStr">
         <is>
           <t>03/01/2036</t>
         </is>
       </c>
-      <c r="T71" s="4" t="inlineStr">
+      <c r="V71" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/stl1.html</t>
         </is>
@@ -7781,55 +8493,65 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
+          <t>St. Lucie County</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>12111</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="L72" s="3" t="inlineStr">
+      <c r="N72" s="3" t="inlineStr">
         <is>
           <t>NPF-16</t>
         </is>
       </c>
-      <c r="M72" s="3" t="inlineStr">
+      <c r="O72" s="3" t="inlineStr">
         <is>
           <t>05000389</t>
         </is>
       </c>
-      <c r="N72" s="3" t="inlineStr">
+      <c r="P72" s="3" t="inlineStr">
         <is>
           <t>05/02/1977</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
+      <c r="Q72" s="3" t="inlineStr">
         <is>
           <t>04/06/1983</t>
         </is>
       </c>
-      <c r="P72" s="3" t="inlineStr">
+      <c r="R72" s="3" t="inlineStr">
         <is>
           <t>08/08/1983</t>
         </is>
       </c>
-      <c r="Q72" s="3" t="inlineStr">
+      <c r="S72" s="3" t="inlineStr">
         <is>
           <t>10/02/2003</t>
         </is>
       </c>
-      <c r="R72" s="3" t="inlineStr">
+      <c r="T72" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S72" s="3" t="inlineStr">
+      <c r="U72" s="3" t="inlineStr">
         <is>
           <t>04/06/2043</t>
         </is>
       </c>
-      <c r="T72" s="2" t="inlineStr">
+      <c r="V72" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/stl2.html</t>
         </is>
@@ -7883,55 +8605,65 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
+          <t>Salem County</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>34033</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
           <t>PSEG</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
+      <c r="M73" s="4" t="inlineStr">
         <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="N73" s="5" t="inlineStr">
         <is>
           <t>DPR-70</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr">
+      <c r="O73" s="5" t="inlineStr">
         <is>
           <t>05000272</t>
         </is>
       </c>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="P73" s="5" t="inlineStr">
         <is>
           <t>09/25/1968</t>
         </is>
       </c>
-      <c r="O73" s="5" t="inlineStr">
+      <c r="Q73" s="5" t="inlineStr">
         <is>
           <t>12/01/1976</t>
         </is>
       </c>
-      <c r="P73" s="5" t="inlineStr">
+      <c r="R73" s="5" t="inlineStr">
         <is>
           <t>06/30/1977</t>
         </is>
       </c>
-      <c r="Q73" s="5" t="inlineStr">
+      <c r="S73" s="5" t="inlineStr">
         <is>
           <t>06/30/2011</t>
         </is>
       </c>
-      <c r="R73" s="5" t="inlineStr">
+      <c r="T73" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S73" s="5" t="inlineStr">
+      <c r="U73" s="5" t="inlineStr">
         <is>
           <t>08/13/2036</t>
         </is>
       </c>
-      <c r="T73" s="4" t="inlineStr">
+      <c r="V73" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/salm1.html</t>
         </is>
@@ -7985,55 +8717,65 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
+          <t>Salem County</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>34033</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
           <t>PSEG</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="L74" s="3" t="inlineStr">
+      <c r="N74" s="3" t="inlineStr">
         <is>
           <t>DPR-75</t>
         </is>
       </c>
-      <c r="M74" s="3" t="inlineStr">
+      <c r="O74" s="3" t="inlineStr">
         <is>
           <t>05000311</t>
         </is>
       </c>
-      <c r="N74" s="3" t="inlineStr">
+      <c r="P74" s="3" t="inlineStr">
         <is>
           <t>09/25/1968</t>
         </is>
       </c>
-      <c r="O74" s="3" t="inlineStr">
+      <c r="Q74" s="3" t="inlineStr">
         <is>
           <t>05/20/1981</t>
         </is>
       </c>
-      <c r="P74" s="3" t="inlineStr">
+      <c r="R74" s="3" t="inlineStr">
         <is>
           <t>10/13/1981</t>
         </is>
       </c>
-      <c r="Q74" s="3" t="inlineStr">
+      <c r="S74" s="3" t="inlineStr">
         <is>
           <t>06/30/2011</t>
         </is>
       </c>
-      <c r="R74" s="3" t="inlineStr">
+      <c r="T74" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S74" s="3" t="inlineStr">
+      <c r="U74" s="3" t="inlineStr">
         <is>
           <t>04/18/2040</t>
         </is>
       </c>
-      <c r="T74" s="2" t="inlineStr">
+      <c r="V74" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/salm2.html</t>
         </is>
@@ -8087,55 +8829,65 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
+          <t>Rockingham County</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>33015</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="K75" s="4" t="inlineStr">
+      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>UE&amp;C</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="N75" s="5" t="inlineStr">
         <is>
           <t>NPF-86</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="O75" s="5" t="inlineStr">
         <is>
           <t>05000443</t>
         </is>
       </c>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="P75" s="5" t="inlineStr">
         <is>
           <t>07/07/1976</t>
         </is>
       </c>
-      <c r="O75" s="5" t="inlineStr">
+      <c r="Q75" s="5" t="inlineStr">
         <is>
           <t>03/15/1990</t>
         </is>
       </c>
-      <c r="P75" s="5" t="inlineStr">
+      <c r="R75" s="5" t="inlineStr">
         <is>
           <t>08/19/1990</t>
         </is>
       </c>
-      <c r="Q75" s="5" t="inlineStr">
+      <c r="S75" s="5" t="inlineStr">
         <is>
           <t>03/12/2019</t>
         </is>
       </c>
-      <c r="R75" s="5" t="inlineStr">
+      <c r="T75" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S75" s="5" t="inlineStr">
+      <c r="U75" s="5" t="inlineStr">
         <is>
           <t>03/15/2050</t>
         </is>
       </c>
-      <c r="T75" s="4" t="inlineStr">
+      <c r="V75" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/seab1.html</t>
         </is>
@@ -8189,55 +8941,65 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
+          <t>Hamilton County</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>47065</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L76" s="3" t="inlineStr">
+      <c r="N76" s="3" t="inlineStr">
         <is>
           <t>DPR-77</t>
         </is>
       </c>
-      <c r="M76" s="3" t="inlineStr">
+      <c r="O76" s="3" t="inlineStr">
         <is>
           <t>05000327</t>
         </is>
       </c>
-      <c r="N76" s="3" t="inlineStr">
+      <c r="P76" s="3" t="inlineStr">
         <is>
           <t>05/27/1970</t>
         </is>
       </c>
-      <c r="O76" s="3" t="inlineStr">
+      <c r="Q76" s="3" t="inlineStr">
         <is>
           <t>09/17/1980</t>
         </is>
       </c>
-      <c r="P76" s="3" t="inlineStr">
+      <c r="R76" s="3" t="inlineStr">
         <is>
           <t>07/01/1981</t>
         </is>
       </c>
-      <c r="Q76" s="3" t="inlineStr">
+      <c r="S76" s="3" t="inlineStr">
         <is>
           <t>09/24/2015</t>
         </is>
       </c>
-      <c r="R76" s="3" t="inlineStr">
+      <c r="T76" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S76" s="3" t="inlineStr">
+      <c r="U76" s="3" t="inlineStr">
         <is>
           <t>09/17/2040</t>
         </is>
       </c>
-      <c r="T76" s="2" t="inlineStr">
+      <c r="V76" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/seq1.html</t>
         </is>
@@ -8291,55 +9053,65 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
+          <t>Hamilton County</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>47065</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
+      <c r="M77" s="4" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L77" s="5" t="inlineStr">
+      <c r="N77" s="5" t="inlineStr">
         <is>
           <t>DPR-79</t>
         </is>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="O77" s="5" t="inlineStr">
         <is>
           <t>05000328</t>
         </is>
       </c>
-      <c r="N77" s="5" t="inlineStr">
+      <c r="P77" s="5" t="inlineStr">
         <is>
           <t>05/27/1970</t>
         </is>
       </c>
-      <c r="O77" s="5" t="inlineStr">
+      <c r="Q77" s="5" t="inlineStr">
         <is>
           <t>09/15/1981</t>
         </is>
       </c>
-      <c r="P77" s="5" t="inlineStr">
+      <c r="R77" s="5" t="inlineStr">
         <is>
           <t>06/01/1982</t>
         </is>
       </c>
-      <c r="Q77" s="5" t="inlineStr">
+      <c r="S77" s="5" t="inlineStr">
         <is>
           <t>09/28/2015</t>
         </is>
       </c>
-      <c r="R77" s="5" t="inlineStr">
+      <c r="T77" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S77" s="5" t="inlineStr">
+      <c r="U77" s="5" t="inlineStr">
         <is>
           <t>09/15/2041</t>
         </is>
       </c>
-      <c r="T77" s="4" t="inlineStr">
+      <c r="V77" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/seq2.html</t>
         </is>
@@ -8393,55 +9165,65 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
+          <t>Wake County</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>37183</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>DANI</t>
         </is>
       </c>
-      <c r="L78" s="3" t="inlineStr">
+      <c r="N78" s="3" t="inlineStr">
         <is>
           <t>NPF-63</t>
         </is>
       </c>
-      <c r="M78" s="3" t="inlineStr">
+      <c r="O78" s="3" t="inlineStr">
         <is>
           <t>05000400</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr">
+      <c r="P78" s="3" t="inlineStr">
         <is>
           <t>01/27/1978</t>
         </is>
       </c>
-      <c r="O78" s="3" t="inlineStr">
+      <c r="Q78" s="3" t="inlineStr">
         <is>
           <t>10/24/1986</t>
         </is>
       </c>
-      <c r="P78" s="3" t="inlineStr">
+      <c r="R78" s="3" t="inlineStr">
         <is>
           <t>05/02/1987</t>
         </is>
       </c>
-      <c r="Q78" s="3" t="inlineStr">
+      <c r="S78" s="3" t="inlineStr">
         <is>
           <t>12/17/2008</t>
         </is>
       </c>
-      <c r="R78" s="3" t="inlineStr">
+      <c r="T78" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S78" s="3" t="inlineStr">
+      <c r="U78" s="3" t="inlineStr">
         <is>
           <t>10/24/2046</t>
         </is>
       </c>
-      <c r="T78" s="2" t="inlineStr">
+      <c r="V78" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/har1.html</t>
         </is>
@@ -8495,55 +9277,65 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
+          <t>Matagorda County</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>48321</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
+      <c r="M79" s="4" t="inlineStr">
         <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="L79" s="5" t="inlineStr">
+      <c r="N79" s="5" t="inlineStr">
         <is>
           <t>NPF-76</t>
         </is>
       </c>
-      <c r="M79" s="5" t="inlineStr">
+      <c r="O79" s="5" t="inlineStr">
         <is>
           <t>05000498</t>
         </is>
       </c>
-      <c r="N79" s="5" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr">
         <is>
           <t>12/22/1975</t>
         </is>
       </c>
-      <c r="O79" s="5" t="inlineStr">
+      <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>03/22/1988</t>
         </is>
       </c>
-      <c r="P79" s="5" t="inlineStr">
+      <c r="R79" s="5" t="inlineStr">
         <is>
           <t>08/25/1988</t>
         </is>
       </c>
-      <c r="Q79" s="5" t="inlineStr">
+      <c r="S79" s="5" t="inlineStr">
         <is>
           <t>09/28/2017</t>
         </is>
       </c>
-      <c r="R79" s="5" t="inlineStr">
+      <c r="T79" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S79" s="5" t="inlineStr">
+      <c r="U79" s="5" t="inlineStr">
         <is>
           <t>08/20/2047</t>
         </is>
       </c>
-      <c r="T79" s="4" t="inlineStr">
+      <c r="V79" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/stp1.html</t>
         </is>
@@ -8597,55 +9389,65 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
+          <t>Matagorda County</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>48321</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="L80" s="3" t="inlineStr">
+      <c r="N80" s="3" t="inlineStr">
         <is>
           <t>NPF-80</t>
         </is>
       </c>
-      <c r="M80" s="3" t="inlineStr">
+      <c r="O80" s="3" t="inlineStr">
         <is>
           <t>05000499</t>
         </is>
       </c>
-      <c r="N80" s="3" t="inlineStr">
+      <c r="P80" s="3" t="inlineStr">
         <is>
           <t>12/22/1975</t>
         </is>
       </c>
-      <c r="O80" s="3" t="inlineStr">
+      <c r="Q80" s="3" t="inlineStr">
         <is>
           <t>03/28/1989</t>
         </is>
       </c>
-      <c r="P80" s="3" t="inlineStr">
+      <c r="R80" s="3" t="inlineStr">
         <is>
           <t>06/19/1989</t>
         </is>
       </c>
-      <c r="Q80" s="3" t="inlineStr">
+      <c r="S80" s="3" t="inlineStr">
         <is>
           <t>09/28/2017</t>
         </is>
       </c>
-      <c r="R80" s="3" t="inlineStr">
+      <c r="T80" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S80" s="3" t="inlineStr">
+      <c r="U80" s="3" t="inlineStr">
         <is>
           <t>12/15/2048</t>
         </is>
       </c>
-      <c r="T80" s="2" t="inlineStr">
+      <c r="V80" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/stp2.html</t>
         </is>
@@ -8699,55 +9501,65 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
+          <t>Surry County</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>51181</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K81" s="4" t="inlineStr">
+      <c r="M81" s="4" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
+      <c r="N81" s="5" t="inlineStr">
         <is>
           <t>DPR-32</t>
         </is>
       </c>
-      <c r="M81" s="5" t="inlineStr">
+      <c r="O81" s="5" t="inlineStr">
         <is>
           <t>05000280</t>
         </is>
       </c>
-      <c r="N81" s="5" t="inlineStr">
+      <c r="P81" s="5" t="inlineStr">
         <is>
           <t>06/25/1968</t>
         </is>
       </c>
-      <c r="O81" s="5" t="inlineStr">
+      <c r="Q81" s="5" t="inlineStr">
         <is>
           <t>05/25/1972</t>
         </is>
       </c>
-      <c r="P81" s="5" t="inlineStr">
+      <c r="R81" s="5" t="inlineStr">
         <is>
           <t>12/22/1972</t>
         </is>
       </c>
-      <c r="Q81" s="5" t="inlineStr">
+      <c r="S81" s="5" t="inlineStr">
         <is>
           <t>03/20/2003</t>
         </is>
       </c>
-      <c r="R81" s="5" t="inlineStr">
+      <c r="T81" s="5" t="inlineStr">
         <is>
           <t>05/04/2021</t>
         </is>
       </c>
-      <c r="S81" s="5" t="inlineStr">
+      <c r="U81" s="5" t="inlineStr">
         <is>
           <t>05/25/2052</t>
         </is>
       </c>
-      <c r="T81" s="4" t="inlineStr">
+      <c r="V81" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/sur1.html</t>
         </is>
@@ -8801,55 +9613,65 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
+          <t>Surry County</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>51181</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>S&amp;W</t>
         </is>
       </c>
-      <c r="L82" s="3" t="inlineStr">
+      <c r="N82" s="3" t="inlineStr">
         <is>
           <t>DPR-37</t>
         </is>
       </c>
-      <c r="M82" s="3" t="inlineStr">
+      <c r="O82" s="3" t="inlineStr">
         <is>
           <t>05000281</t>
         </is>
       </c>
-      <c r="N82" s="3" t="inlineStr">
+      <c r="P82" s="3" t="inlineStr">
         <is>
           <t>06/25/1968</t>
         </is>
       </c>
-      <c r="O82" s="3" t="inlineStr">
+      <c r="Q82" s="3" t="inlineStr">
         <is>
           <t>01/29/1973</t>
         </is>
       </c>
-      <c r="P82" s="3" t="inlineStr">
+      <c r="R82" s="3" t="inlineStr">
         <is>
           <t>05/01/1973</t>
         </is>
       </c>
-      <c r="Q82" s="3" t="inlineStr">
+      <c r="S82" s="3" t="inlineStr">
         <is>
           <t>03/20/2003</t>
         </is>
       </c>
-      <c r="R82" s="3" t="inlineStr">
+      <c r="T82" s="3" t="inlineStr">
         <is>
           <t>05/04/2021</t>
         </is>
       </c>
-      <c r="S82" s="3" t="inlineStr">
+      <c r="U82" s="3" t="inlineStr">
         <is>
           <t>01/29/2053</t>
         </is>
       </c>
-      <c r="T82" s="2" t="inlineStr">
+      <c r="V82" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/sur2.html</t>
         </is>
@@ -8903,55 +9725,65 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
+          <t>Luzerne County</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>42079</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="M83" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L83" s="5" t="inlineStr">
+      <c r="N83" s="5" t="inlineStr">
         <is>
           <t>NPF-14</t>
         </is>
       </c>
-      <c r="M83" s="5" t="inlineStr">
+      <c r="O83" s="5" t="inlineStr">
         <is>
           <t>05000387</t>
         </is>
       </c>
-      <c r="N83" s="5" t="inlineStr">
+      <c r="P83" s="5" t="inlineStr">
         <is>
           <t>11/03/1973</t>
         </is>
       </c>
-      <c r="O83" s="5" t="inlineStr">
+      <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>07/17/1982</t>
         </is>
       </c>
-      <c r="P83" s="5" t="inlineStr">
+      <c r="R83" s="5" t="inlineStr">
         <is>
           <t>06/08/1983</t>
         </is>
       </c>
-      <c r="Q83" s="5" t="inlineStr">
+      <c r="S83" s="5" t="inlineStr">
         <is>
           <t>11/24/2009</t>
         </is>
       </c>
-      <c r="R83" s="5" t="inlineStr">
+      <c r="T83" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S83" s="5" t="inlineStr">
+      <c r="U83" s="5" t="inlineStr">
         <is>
           <t>07/17/2042</t>
         </is>
       </c>
-      <c r="T83" s="4" t="inlineStr">
+      <c r="V83" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/susq1.html</t>
         </is>
@@ -9005,55 +9837,65 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
+          <t>Luzerne County</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>42079</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L84" s="3" t="inlineStr">
+      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>NPF-22</t>
         </is>
       </c>
-      <c r="M84" s="3" t="inlineStr">
+      <c r="O84" s="3" t="inlineStr">
         <is>
           <t>05000388</t>
         </is>
       </c>
-      <c r="N84" s="3" t="inlineStr">
+      <c r="P84" s="3" t="inlineStr">
         <is>
           <t>11/03/1973</t>
         </is>
       </c>
-      <c r="O84" s="3" t="inlineStr">
+      <c r="Q84" s="3" t="inlineStr">
         <is>
           <t>03/23/1984</t>
         </is>
       </c>
-      <c r="P84" s="3" t="inlineStr">
+      <c r="R84" s="3" t="inlineStr">
         <is>
           <t>02/12/1985</t>
         </is>
       </c>
-      <c r="Q84" s="3" t="inlineStr">
+      <c r="S84" s="3" t="inlineStr">
         <is>
           <t>11/24/2009</t>
         </is>
       </c>
-      <c r="R84" s="3" t="inlineStr">
+      <c r="T84" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S84" s="3" t="inlineStr">
+      <c r="U84" s="3" t="inlineStr">
         <is>
           <t>03/23/2044</t>
         </is>
       </c>
-      <c r="T84" s="2" t="inlineStr">
+      <c r="V84" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/susq2.html</t>
         </is>
@@ -9107,55 +9949,65 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K85" s="4" t="inlineStr">
+      <c r="M85" s="4" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L85" s="5" t="inlineStr">
+      <c r="N85" s="5" t="inlineStr">
         <is>
           <t>DPR-31</t>
         </is>
       </c>
-      <c r="M85" s="5" t="inlineStr">
+      <c r="O85" s="5" t="inlineStr">
         <is>
           <t>05000250</t>
         </is>
       </c>
-      <c r="N85" s="5" t="inlineStr">
+      <c r="P85" s="5" t="inlineStr">
         <is>
           <t>04/27/1967</t>
         </is>
       </c>
-      <c r="O85" s="5" t="inlineStr">
+      <c r="Q85" s="5" t="inlineStr">
         <is>
           <t>07/19/1972</t>
         </is>
       </c>
-      <c r="P85" s="5" t="inlineStr">
+      <c r="R85" s="5" t="inlineStr">
         <is>
           <t>12/14/1972</t>
         </is>
       </c>
-      <c r="Q85" s="5" t="inlineStr">
+      <c r="S85" s="5" t="inlineStr">
         <is>
           <t>06/06/2002</t>
         </is>
       </c>
-      <c r="R85" s="5" t="inlineStr">
+      <c r="T85" s="5" t="inlineStr">
         <is>
           <t>12/04/2019</t>
         </is>
       </c>
-      <c r="S85" s="5" t="inlineStr">
+      <c r="U85" s="5" t="inlineStr">
         <is>
           <t>07/19/2052</t>
         </is>
       </c>
-      <c r="T85" s="4" t="inlineStr">
+      <c r="V85" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/tp3.html</t>
         </is>
@@ -9209,55 +10061,65 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="L86" s="3" t="inlineStr">
+      <c r="N86" s="3" t="inlineStr">
         <is>
           <t>DPR-41</t>
         </is>
       </c>
-      <c r="M86" s="3" t="inlineStr">
+      <c r="O86" s="3" t="inlineStr">
         <is>
           <t>05000251</t>
         </is>
       </c>
-      <c r="N86" s="3" t="inlineStr">
+      <c r="P86" s="3" t="inlineStr">
         <is>
           <t>04/27/1967</t>
         </is>
       </c>
-      <c r="O86" s="3" t="inlineStr">
+      <c r="Q86" s="3" t="inlineStr">
         <is>
           <t>04/10/1973</t>
         </is>
       </c>
-      <c r="P86" s="3" t="inlineStr">
+      <c r="R86" s="3" t="inlineStr">
         <is>
           <t>09/07/1973</t>
         </is>
       </c>
-      <c r="Q86" s="3" t="inlineStr">
+      <c r="S86" s="3" t="inlineStr">
         <is>
           <t>06/06/2002</t>
         </is>
       </c>
-      <c r="R86" s="3" t="inlineStr">
+      <c r="T86" s="3" t="inlineStr">
         <is>
           <t>12/04/2019</t>
         </is>
       </c>
-      <c r="S86" s="3" t="inlineStr">
+      <c r="U86" s="3" t="inlineStr">
         <is>
           <t>04/10/2053</t>
         </is>
       </c>
-      <c r="T86" s="2" t="inlineStr">
+      <c r="V86" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/tp4.html</t>
         </is>
@@ -9311,55 +10173,65 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
+          <t>Fairfield County</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>45039</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
           <t>GIL</t>
         </is>
       </c>
-      <c r="K87" s="4" t="inlineStr">
+      <c r="M87" s="4" t="inlineStr">
         <is>
           <t>DANI</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="N87" s="5" t="inlineStr">
         <is>
           <t>NPF-12</t>
         </is>
       </c>
-      <c r="M87" s="5" t="inlineStr">
+      <c r="O87" s="5" t="inlineStr">
         <is>
           <t>05000395</t>
         </is>
       </c>
-      <c r="N87" s="5" t="inlineStr">
+      <c r="P87" s="5" t="inlineStr">
         <is>
           <t>03/21/1973</t>
         </is>
       </c>
-      <c r="O87" s="5" t="inlineStr">
+      <c r="Q87" s="5" t="inlineStr">
         <is>
           <t>11/12/1982</t>
         </is>
       </c>
-      <c r="P87" s="5" t="inlineStr">
+      <c r="R87" s="5" t="inlineStr">
         <is>
           <t>01/01/1984</t>
         </is>
       </c>
-      <c r="Q87" s="5" t="inlineStr">
+      <c r="S87" s="5" t="inlineStr">
         <is>
           <t>04/23/2004</t>
         </is>
       </c>
-      <c r="R87" s="5" t="inlineStr">
+      <c r="T87" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S87" s="5" t="inlineStr">
+      <c r="U87" s="5" t="inlineStr">
         <is>
           <t>08/06/2042</t>
         </is>
       </c>
-      <c r="T87" s="4" t="inlineStr">
+      <c r="V87" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/sum.html</t>
         </is>
@@ -9413,55 +10285,65 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
+          <t>Burke County</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
           <t>SBEC</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>GPC</t>
         </is>
       </c>
-      <c r="L88" s="3" t="inlineStr">
+      <c r="N88" s="3" t="inlineStr">
         <is>
           <t>NPF-68</t>
         </is>
       </c>
-      <c r="M88" s="3" t="inlineStr">
+      <c r="O88" s="3" t="inlineStr">
         <is>
           <t>05000424</t>
         </is>
       </c>
-      <c r="N88" s="3" t="inlineStr">
+      <c r="P88" s="3" t="inlineStr">
         <is>
           <t>06/28/1974</t>
         </is>
       </c>
-      <c r="O88" s="3" t="inlineStr">
+      <c r="Q88" s="3" t="inlineStr">
         <is>
           <t>03/16/1987</t>
         </is>
       </c>
-      <c r="P88" s="3" t="inlineStr">
+      <c r="R88" s="3" t="inlineStr">
         <is>
           <t>06/01/1987</t>
         </is>
       </c>
-      <c r="Q88" s="3" t="inlineStr">
+      <c r="S88" s="3" t="inlineStr">
         <is>
           <t>06/03/2009</t>
         </is>
       </c>
-      <c r="R88" s="3" t="inlineStr">
+      <c r="T88" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S88" s="3" t="inlineStr">
+      <c r="U88" s="3" t="inlineStr">
         <is>
           <t>01/16/2047</t>
         </is>
       </c>
-      <c r="T88" s="2" t="inlineStr">
+      <c r="V88" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/vog1.html</t>
         </is>
@@ -9515,55 +10397,65 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
+          <t>Burke County</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
           <t>SBEC</t>
         </is>
       </c>
-      <c r="K89" s="4" t="inlineStr">
+      <c r="M89" s="4" t="inlineStr">
         <is>
           <t>GPC</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
+      <c r="N89" s="5" t="inlineStr">
         <is>
           <t>NPF-81</t>
         </is>
       </c>
-      <c r="M89" s="5" t="inlineStr">
+      <c r="O89" s="5" t="inlineStr">
         <is>
           <t>05000425</t>
         </is>
       </c>
-      <c r="N89" s="5" t="inlineStr">
+      <c r="P89" s="5" t="inlineStr">
         <is>
           <t>06/28/1974</t>
         </is>
       </c>
-      <c r="O89" s="5" t="inlineStr">
+      <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>03/31/1989</t>
         </is>
       </c>
-      <c r="P89" s="5" t="inlineStr">
+      <c r="R89" s="5" t="inlineStr">
         <is>
           <t>05/20/1989</t>
         </is>
       </c>
-      <c r="Q89" s="5" t="inlineStr">
+      <c r="S89" s="5" t="inlineStr">
         <is>
           <t>06/03/2009</t>
         </is>
       </c>
-      <c r="R89" s="5" t="inlineStr">
+      <c r="T89" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S89" s="5" t="inlineStr">
+      <c r="U89" s="5" t="inlineStr">
         <is>
           <t>02/09/2049</t>
         </is>
       </c>
-      <c r="T89" s="4" t="inlineStr">
+      <c r="V89" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/vog2.html</t>
         </is>
@@ -9617,35 +10509,45 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
+          <t>Burke County</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
           <t>WEST 2LP</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="3" t="inlineStr"/>
-      <c r="M90" s="3" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr">
         <is>
           <t>05200025</t>
         </is>
       </c>
-      <c r="N90" s="3" t="inlineStr">
+      <c r="P90" s="3" t="inlineStr">
         <is>
           <t>02/10/2012</t>
         </is>
       </c>
-      <c r="O90" s="3" t="inlineStr">
+      <c r="Q90" s="3" t="inlineStr">
         <is>
           <t>08/03/2022</t>
         </is>
       </c>
-      <c r="P90" s="3" t="inlineStr"/>
-      <c r="Q90" s="3" t="inlineStr"/>
-      <c r="R90" s="3" t="inlineStr">
+      <c r="R90" s="3" t="inlineStr"/>
+      <c r="S90" s="3" t="inlineStr"/>
+      <c r="T90" s="3" t="inlineStr">
         <is>
           <t>08/03/2062</t>
         </is>
       </c>
-      <c r="S90" s="3" t="inlineStr"/>
-      <c r="T90" s="2" t="inlineStr">
+      <c r="U90" s="3" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/col-holder/vog3.html</t>
         </is>
@@ -9699,35 +10601,45 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
+          <t>Burke County</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
           <t>WEST 2LP</t>
         </is>
       </c>
-      <c r="K91" s="4" t="inlineStr"/>
-      <c r="L91" s="5" t="inlineStr"/>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="M91" s="4" t="inlineStr"/>
+      <c r="N91" s="5" t="inlineStr"/>
+      <c r="O91" s="5" t="inlineStr">
         <is>
           <t>05200026</t>
         </is>
       </c>
-      <c r="N91" s="5" t="inlineStr">
+      <c r="P91" s="5" t="inlineStr">
         <is>
           <t>02/10/2012</t>
         </is>
       </c>
-      <c r="O91" s="5" t="inlineStr">
+      <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>07/28/2023</t>
         </is>
       </c>
-      <c r="P91" s="5" t="inlineStr"/>
-      <c r="Q91" s="5" t="inlineStr"/>
-      <c r="R91" s="5" t="inlineStr">
+      <c r="R91" s="5" t="inlineStr"/>
+      <c r="S91" s="5" t="inlineStr"/>
+      <c r="T91" s="5" t="inlineStr">
         <is>
           <t>7/28/2063</t>
         </is>
       </c>
-      <c r="S91" s="5" t="inlineStr"/>
-      <c r="T91" s="4" t="inlineStr">
+      <c r="U91" s="5" t="inlineStr"/>
+      <c r="V91" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/col-holder/vog4.html</t>
         </is>
@@ -9781,55 +10693,65 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
+          <t>St. Charles Parish</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>22089</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>EBSO</t>
         </is>
       </c>
-      <c r="L92" s="3" t="inlineStr">
+      <c r="N92" s="3" t="inlineStr">
         <is>
           <t>NPF-38</t>
         </is>
       </c>
-      <c r="M92" s="3" t="inlineStr">
+      <c r="O92" s="3" t="inlineStr">
         <is>
           <t>05000382</t>
         </is>
       </c>
-      <c r="N92" s="3" t="inlineStr">
+      <c r="P92" s="3" t="inlineStr">
         <is>
           <t>11/14/1974</t>
         </is>
       </c>
-      <c r="O92" s="3" t="inlineStr">
+      <c r="Q92" s="3" t="inlineStr">
         <is>
           <t>03/16/1985</t>
         </is>
       </c>
-      <c r="P92" s="3" t="inlineStr">
+      <c r="R92" s="3" t="inlineStr">
         <is>
           <t>09/24/1985</t>
         </is>
       </c>
-      <c r="Q92" s="3" t="inlineStr">
+      <c r="S92" s="3" t="inlineStr">
         <is>
           <t>12/27/2018</t>
         </is>
       </c>
-      <c r="R92" s="3" t="inlineStr">
+      <c r="T92" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S92" s="3" t="inlineStr">
+      <c r="U92" s="3" t="inlineStr">
         <is>
           <t>12/18/2044</t>
         </is>
       </c>
-      <c r="T92" s="2" t="inlineStr">
+      <c r="V92" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/wat3.html</t>
         </is>
@@ -9883,55 +10805,65 @@
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
+          <t>Rhea County</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>47143</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="K93" s="4" t="inlineStr">
+      <c r="M93" s="4" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L93" s="5" t="inlineStr">
+      <c r="N93" s="5" t="inlineStr">
         <is>
           <t>NPF-90</t>
         </is>
       </c>
-      <c r="M93" s="5" t="inlineStr">
+      <c r="O93" s="5" t="inlineStr">
         <is>
           <t>05000390</t>
         </is>
       </c>
-      <c r="N93" s="5" t="inlineStr">
+      <c r="P93" s="5" t="inlineStr">
         <is>
           <t>01/23/1973</t>
         </is>
       </c>
-      <c r="O93" s="5" t="inlineStr">
+      <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>02/07/1996</t>
         </is>
       </c>
-      <c r="P93" s="5" t="inlineStr">
+      <c r="R93" s="5" t="inlineStr">
         <is>
           <t>05/27/1996</t>
         </is>
       </c>
-      <c r="Q93" s="5" t="inlineStr">
+      <c r="S93" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R93" s="5" t="inlineStr">
+      <c r="T93" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S93" s="5" t="inlineStr">
+      <c r="U93" s="5" t="inlineStr">
         <is>
           <t>11/09/2035</t>
         </is>
       </c>
-      <c r="T93" s="4" t="inlineStr">
+      <c r="V93" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/wb1.html</t>
         </is>
@@ -9985,55 +10917,65 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
+          <t>Rhea County</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>47143</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L94" s="3" t="inlineStr">
+      <c r="N94" s="3" t="inlineStr">
         <is>
           <t>NPF-96</t>
         </is>
       </c>
-      <c r="M94" s="3" t="inlineStr">
+      <c r="O94" s="3" t="inlineStr">
         <is>
           <t>05000391</t>
         </is>
       </c>
-      <c r="N94" s="3" t="inlineStr">
+      <c r="P94" s="3" t="inlineStr">
         <is>
           <t>01/24/1973</t>
         </is>
       </c>
-      <c r="O94" s="3" t="inlineStr">
+      <c r="Q94" s="3" t="inlineStr">
         <is>
           <t>10/22/2015</t>
         </is>
       </c>
-      <c r="P94" s="3" t="inlineStr">
+      <c r="R94" s="3" t="inlineStr">
         <is>
           <t>10/19/2016</t>
         </is>
       </c>
-      <c r="Q94" s="3" t="inlineStr">
+      <c r="S94" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R94" s="3" t="inlineStr">
+      <c r="T94" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S94" s="3" t="inlineStr">
+      <c r="U94" s="3" t="inlineStr">
         <is>
           <t>10/22/2055</t>
         </is>
       </c>
-      <c r="T94" s="2" t="inlineStr">
+      <c r="V94" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/wb2.html</t>
         </is>
@@ -10083,62 +11025,72 @@
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
+          <t>Coffey County</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>20031</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
           <t>BECH</t>
         </is>
       </c>
-      <c r="K95" s="4" t="inlineStr">
+      <c r="M95" s="4" t="inlineStr">
         <is>
           <t>DANI</t>
         </is>
       </c>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="N95" s="5" t="inlineStr">
         <is>
           <t>NPF-42</t>
         </is>
       </c>
-      <c r="M95" s="5" t="inlineStr">
+      <c r="O95" s="5" t="inlineStr">
         <is>
           <t>05000482</t>
         </is>
       </c>
-      <c r="N95" s="5" t="inlineStr">
+      <c r="P95" s="5" t="inlineStr">
         <is>
           <t>05/17/1977</t>
         </is>
       </c>
-      <c r="O95" s="5" t="inlineStr">
+      <c r="Q95" s="5" t="inlineStr">
         <is>
           <t>06/04/1985F</t>
         </is>
       </c>
-      <c r="P95" s="5" t="inlineStr">
+      <c r="R95" s="5" t="inlineStr">
         <is>
           <t>09/03/1985</t>
         </is>
       </c>
-      <c r="Q95" s="5" t="inlineStr">
+      <c r="S95" s="5" t="inlineStr">
         <is>
           <t>11/20/2008</t>
         </is>
       </c>
-      <c r="R95" s="5" t="inlineStr">
+      <c r="T95" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S95" s="5" t="inlineStr">
+      <c r="U95" s="5" t="inlineStr">
         <is>
           <t>03/11/2045</t>
         </is>
       </c>
-      <c r="T95" s="4" t="inlineStr">
+      <c r="V95" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/info-finder/reactors/wc.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T95"/>
+  <autoFilter ref="A1:V95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10149,7 +11101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10161,13 +11113,15 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="46" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -10218,35 +11172,45 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>FIPS Code</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Architect Engineer</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Constructor</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>License Number</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Docket Number</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CP Issued</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>COL Issued</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>NRC Web Page</t>
         </is>
@@ -10290,25 +11254,35 @@
           <t>(6 miles NE of Scottsboro, AL)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Jackson County</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>01071</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>05000438</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>12/24/1974</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/bellefonte-constr-permits.html</t>
         </is>
@@ -10352,25 +11326,35 @@
           <t>(6 miles NE of Scottsboro, AL)</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Jackson County</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>01071</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>05000439</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>12/24/1974</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/bellefonte-constr-permits.html</t>
         </is>
@@ -10418,21 +11402,31 @@
           <t>(25 miles NE of Toledo, OH)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Monroe County</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>26115</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>NPF-95</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>05/01/2015</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/col-holder/ferm3.html</t>
         </is>
@@ -10482,23 +11476,33 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
+          <t>Louisa County</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>51109</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
           <t>GEH</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>NPF-103</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>06/02/2017</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/col-holder/na3.html</t>
         </is>
@@ -10548,23 +11552,33 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>WEST 2LP</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>NPF-104</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>04/12/2018</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/col-holder/tp6.html</t>
         </is>
@@ -10614,23 +11628,33 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
+          <t>Miami-Dade County</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
           <t>WEST 2LP</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>NPF-105</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>04/12/2018</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/col-holder/tp7.html</t>
         </is>
@@ -10680,23 +11704,33 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>Cherokee County</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>45021</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>WEST 2LP</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>NPF-101</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>12/19/2016</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/col-holder/lee1.html</t>
         </is>
@@ -10746,30 +11780,40 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
+          <t>Cherokee County</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>45021</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
           <t>WEST 2LP</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>NPF-102</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>12/19/2016</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>https://www.nrc.gov/reactors/new-reactors/col-holder/lee2.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:R9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>